--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0002T0006Z000C1N96_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0002T0006Z000C1N96_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>40.69705149024927</v>
+        <v>6.613270867165506</v>
       </c>
       <c r="D2" t="n">
-        <v>39.23572373969059</v>
+        <v>6.375805107699722</v>
       </c>
       <c r="E2" t="n">
-        <v>13.88613161819772</v>
+        <v>2.256496387957131</v>
       </c>
       <c r="F2" t="n">
-        <v>17.05535077878003</v>
+        <v>2.771494501551755</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>10.2796479901129</v>
+        <v>1.670442798393347</v>
       </c>
       <c r="D3" t="n">
-        <v>54.88624600025037</v>
+        <v>8.919014975040685</v>
       </c>
       <c r="E3" t="n">
-        <v>13.88613161819772</v>
+        <v>2.256496387957131</v>
       </c>
       <c r="F3" t="n">
-        <v>17.05535077878003</v>
+        <v>2.771494501551755</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>1.3</v>
       </c>
       <c r="D4" t="n">
-        <v>23.57292668280999</v>
+        <v>3.830600585956624</v>
       </c>
       <c r="E4" t="n">
-        <v>13.88613161819772</v>
+        <v>2.256496387957131</v>
       </c>
       <c r="F4" t="n">
-        <v>17.05535077878003</v>
+        <v>2.771494501551755</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>29.20703109460209</v>
+        <v>4.746142552872841</v>
       </c>
       <c r="D5" t="n">
-        <v>25.11513346023225</v>
+        <v>4.08120918728774</v>
       </c>
       <c r="E5" t="n">
-        <v>13.88613161819772</v>
+        <v>2.256496387957131</v>
       </c>
       <c r="F5" t="n">
-        <v>17.05535077878003</v>
+        <v>2.771494501551755</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>29.48025212941655</v>
+        <v>4.79054097103019</v>
       </c>
       <c r="D6" t="n">
-        <v>30.92217613917778</v>
+        <v>5.024853622616389</v>
       </c>
       <c r="E6" t="n">
-        <v>13.88613161819772</v>
+        <v>2.256496387957131</v>
       </c>
       <c r="F6" t="n">
-        <v>17.05535077878003</v>
+        <v>2.771494501551755</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>1.265489850791738</v>
+        <v>0.2056421007536574</v>
       </c>
       <c r="D7" t="n">
-        <v>47.99753514697767</v>
+        <v>7.799599461383871</v>
       </c>
       <c r="E7" t="n">
-        <v>13.88613161819772</v>
+        <v>2.256496387957131</v>
       </c>
       <c r="F7" t="n">
-        <v>17.05535077878003</v>
+        <v>2.771494501551755</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>23.17432761205989</v>
+        <v>3.765828236959733</v>
       </c>
       <c r="D8" t="n">
-        <v>12.5</v>
+        <v>2.03125</v>
       </c>
       <c r="E8" t="n">
-        <v>13.88613161819772</v>
+        <v>2.256496387957131</v>
       </c>
       <c r="F8" t="n">
-        <v>17.05535077878003</v>
+        <v>2.771494501551755</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>37.5</v>
+        <v>6.09375</v>
       </c>
       <c r="D9" t="n">
-        <v>59.51280940378626</v>
+        <v>9.670831528115267</v>
       </c>
       <c r="E9" t="n">
-        <v>13.88613161819772</v>
+        <v>2.256496387957131</v>
       </c>
       <c r="F9" t="n">
-        <v>17.05535077878003</v>
+        <v>2.771494501551755</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>27.70558797118832</v>
+        <v>4.502158045318102</v>
       </c>
       <c r="D10" t="n">
-        <v>35.34134632361099</v>
+        <v>5.742968777586786</v>
       </c>
       <c r="E10" t="n">
-        <v>13.88613161819772</v>
+        <v>2.256496387957131</v>
       </c>
       <c r="F10" t="n">
-        <v>17.05535077878003</v>
+        <v>2.771494501551755</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>45.69737410398983</v>
+        <v>7.425823291898348</v>
       </c>
       <c r="D11" t="n">
-        <v>67.14284572054969</v>
+        <v>10.91071242958932</v>
       </c>
       <c r="E11" t="n">
-        <v>13.88613161819772</v>
+        <v>2.256496387957131</v>
       </c>
       <c r="F11" t="n">
-        <v>17.05535077878003</v>
+        <v>2.771494501551755</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>17.07250293083987</v>
+        <v>2.774281726261479</v>
       </c>
       <c r="D12" t="n">
-        <v>17.19656673040518</v>
+        <v>2.794442093690843</v>
       </c>
       <c r="E12" t="n">
-        <v>13.88613161819772</v>
+        <v>2.256496387957131</v>
       </c>
       <c r="F12" t="n">
-        <v>17.05535077878003</v>
+        <v>2.771494501551755</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>25.96870974798769</v>
+        <v>4.219915334048</v>
       </c>
       <c r="D13" t="n">
-        <v>33.85945327628392</v>
+        <v>5.502161157396138</v>
       </c>
       <c r="E13" t="n">
-        <v>13.88613161819772</v>
+        <v>2.256496387957131</v>
       </c>
       <c r="F13" t="n">
-        <v>17.05535077878003</v>
+        <v>2.771494501551755</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>25.521959260279</v>
+        <v>4.147318379795339</v>
       </c>
       <c r="D14" t="n">
-        <v>31.21601083104006</v>
+        <v>5.072601760044009</v>
       </c>
       <c r="E14" t="n">
-        <v>13.88613161819772</v>
+        <v>2.256496387957131</v>
       </c>
       <c r="F14" t="n">
-        <v>17.05535077878003</v>
+        <v>2.771494501551755</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>53.41598854881806</v>
+        <v>8.680098139182936</v>
       </c>
       <c r="D15" t="n">
-        <v>72.66635130012105</v>
+        <v>11.80828208626967</v>
       </c>
       <c r="E15" t="n">
-        <v>13.88613161819772</v>
+        <v>2.256496387957131</v>
       </c>
       <c r="F15" t="n">
-        <v>17.05535077878003</v>
+        <v>2.771494501551755</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>28.96884506111969</v>
+        <v>4.70743732243195</v>
       </c>
       <c r="D16" t="n">
-        <v>32.27687175020932</v>
+        <v>5.244991659409014</v>
       </c>
       <c r="E16" t="n">
-        <v>13.88613161819772</v>
+        <v>2.256496387957131</v>
       </c>
       <c r="F16" t="n">
-        <v>17.05535077878003</v>
+        <v>2.771494501551755</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>44.51112282193839</v>
+        <v>7.233057458564989</v>
       </c>
       <c r="D17" t="n">
-        <v>57.62011841336722</v>
+        <v>9.363269242172175</v>
       </c>
       <c r="E17" t="n">
-        <v>13.88613161819772</v>
+        <v>2.256496387957131</v>
       </c>
       <c r="F17" t="n">
-        <v>17.05535077878003</v>
+        <v>2.771494501551755</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>13.14882015252229</v>
+        <v>2.136683274784872</v>
       </c>
       <c r="D18" t="n">
-        <v>28.88583322333622</v>
+        <v>4.693947898792136</v>
       </c>
       <c r="E18" t="n">
-        <v>13.88613161819772</v>
+        <v>2.256496387957131</v>
       </c>
       <c r="F18" t="n">
-        <v>17.05535077878003</v>
+        <v>2.771494501551755</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
